--- a/ONCHO/Entomological survey Survey/Nigeria/2026/ng_oncho_2601_4_b_lab_tar.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2026/ng_oncho_2601_4_b_lab_tar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3958B2-A411-4532-A198-8E7E2A8E7497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779D2E7C-D549-4C10-84D3-4E1157334EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="137">
   <si>
     <t>type</t>
   </si>
@@ -412,9 +412,6 @@
     <t>12. Which type of test was performed on this pool?</t>
   </si>
   <si>
-    <t>13. Number of heads in the pool tested</t>
-  </si>
-  <si>
     <t>14. Result for BAC</t>
   </si>
   <si>
@@ -428,6 +425,27 @@
   </si>
   <si>
     <t>selected(${test_type}, 'qPCR')</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>calculate</t>
+  </si>
+  <si>
+    <t>position(..)</t>
+  </si>
+  <si>
+    <t>pool_idx</t>
+  </si>
+  <si>
+    <t>13. Number of heads in Pool #${pool_idx}</t>
+  </si>
+  <si>
+    <t>. &lt;= 200</t>
+  </si>
+  <si>
+    <t>The number of pools is limited to 200</t>
   </si>
 </sst>
 </file>
@@ -706,87 +724,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1236,7 +1174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.625" style="3" customWidth="1"/>
@@ -1612,8 +1550,12 @@
       </c>
       <c r="D12" s="28"/>
       <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="28"/>
+      <c r="F12" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>136</v>
+      </c>
       <c r="H12" s="26"/>
       <c r="I12" s="26"/>
       <c r="J12" s="26" t="s">
@@ -1648,39 +1590,37 @@
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:26" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="26" t="s">
-        <v>95</v>
+    <row r="14" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>131</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>124</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="C14" s="28"/>
       <c r="D14" s="28"/>
       <c r="E14" s="26"/>
       <c r="F14" s="26"/>
       <c r="G14" s="28"/>
       <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26" t="s">
-        <v>9</v>
-      </c>
+      <c r="I14" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="J14" s="26"/>
       <c r="K14" s="26"/>
       <c r="L14" s="26"/>
       <c r="M14" s="26"/>
       <c r="N14" s="26"/>
     </row>
-    <row r="15" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D15" s="28"/>
       <c r="E15" s="26"/>
@@ -1696,23 +1636,21 @@
       <c r="M15" s="26"/>
       <c r="N15" s="26"/>
     </row>
-    <row r="16" spans="1:26" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D16" s="28"/>
       <c r="E16" s="26"/>
       <c r="F16" s="26"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="26" t="s">
-        <v>130</v>
-      </c>
+      <c r="H16" s="26"/>
       <c r="I16" s="26"/>
       <c r="J16" s="26" t="s">
         <v>9</v>
@@ -1727,16 +1665,18 @@
         <v>100</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D17" s="28"/>
       <c r="E17" s="26"/>
       <c r="F17" s="26"/>
       <c r="G17" s="28"/>
-      <c r="H17" s="26"/>
+      <c r="H17" s="26" t="s">
+        <v>129</v>
+      </c>
       <c r="I17" s="26"/>
       <c r="J17" s="26" t="s">
         <v>9</v>
@@ -1751,93 +1691,97 @@
         <v>100</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D18" s="28"/>
       <c r="E18" s="26"/>
       <c r="F18" s="26"/>
       <c r="G18" s="28"/>
-      <c r="H18" s="26" t="s">
-        <v>130</v>
-      </c>
+      <c r="H18" s="26"/>
       <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
+      <c r="J18" s="26" t="s">
+        <v>9</v>
+      </c>
       <c r="K18" s="26"/>
       <c r="L18" s="26"/>
       <c r="M18" s="26"/>
       <c r="N18" s="26"/>
     </row>
-    <row r="19" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D19" s="28"/>
       <c r="E19" s="26"/>
       <c r="F19" s="26"/>
       <c r="G19" s="28"/>
-      <c r="H19" s="26"/>
+      <c r="H19" s="26" t="s">
+        <v>129</v>
+      </c>
       <c r="I19" s="26"/>
-      <c r="J19" s="26" t="s">
-        <v>9</v>
-      </c>
+      <c r="J19" s="26"/>
       <c r="K19" s="26"/>
       <c r="L19" s="26"/>
       <c r="M19" s="26"/>
       <c r="N19" s="26"/>
     </row>
     <row r="20" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="28"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+    </row>
+    <row r="21" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-    </row>
-    <row r="21" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
     </row>
     <row r="22" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" s="32"/>
       <c r="D22" s="32"/>
@@ -1851,6 +1795,26 @@
       <c r="L22" s="33"/>
       <c r="M22" s="33"/>
       <c r="N22" s="33"/>
+    </row>
+    <row r="23" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+      <c r="N23" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3982,29 +3946,29 @@
       <c r="D328" s="13"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B53:B147">
-    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148:B160">
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B161:B167">
-    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13">
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19:C28">
+    <cfRule type="duplicateValues" dxfId="2" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218:C263">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C19:C28">
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C13">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/ONCHO/Entomological survey Survey/Nigeria/2026/ng_oncho_2601_4_b_lab_tar.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2026/ng_oncho_2601_4_b_lab_tar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779D2E7C-D549-4C10-84D3-4E1157334EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55E796E-F70C-4EBC-946C-97115F6608EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -322,9 +322,6 @@
     <t>PCR ELISA</t>
   </si>
   <si>
-    <t>select_multiple type_test</t>
-  </si>
-  <si>
     <t>BAC</t>
   </si>
   <si>
@@ -442,10 +439,13 @@
     <t>13. Number of heads in Pool #${pool_idx}</t>
   </si>
   <si>
-    <t>. &lt;= 200</t>
-  </si>
-  <si>
-    <t>The number of pools is limited to 200</t>
+    <t>select_one type_test</t>
+  </si>
+  <si>
+    <t>. &gt; 0 and . &lt;= 200</t>
+  </si>
+  <si>
+    <t>The number of pools must between 1 and 200 inclusive</t>
   </si>
 </sst>
 </file>
@@ -1283,10 +1283,10 @@
         <v>20</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
@@ -1316,13 +1316,13 @@
     </row>
     <row r="4" spans="1:26" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
@@ -1352,13 +1352,13 @@
     </row>
     <row r="5" spans="1:26" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -1394,7 +1394,7 @@
         <v>34</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6" s="28"/>
       <c r="E6" s="26"/>
@@ -1418,7 +1418,7 @@
         <v>56</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D7" s="28"/>
       <c r="E7" s="26"/>
@@ -1441,10 +1441,10 @@
         <v>65</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D8" s="28"/>
       <c r="E8" s="26"/>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="9" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D9" s="28"/>
       <c r="E9" s="26"/>
@@ -1494,7 +1494,7 @@
         <v>36</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D10" s="28"/>
       <c r="E10" s="26"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="K10" s="26"/>
       <c r="L10" s="26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M10" s="26"/>
       <c r="N10" s="26"/>
@@ -1520,7 +1520,7 @@
         <v>58</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D11" s="28" t="s">
         <v>59</v>
@@ -1543,19 +1543,15 @@
         <v>20</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D12" s="28"/>
       <c r="E12" s="26"/>
-      <c r="F12" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>136</v>
-      </c>
+      <c r="F12" s="26"/>
+      <c r="G12" s="28"/>
       <c r="H12" s="26"/>
       <c r="I12" s="26"/>
       <c r="J12" s="26" t="s">
@@ -1587,15 +1583,15 @@
       <c r="L13" s="29"/>
       <c r="M13" s="29"/>
       <c r="N13" s="29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C14" s="28"/>
       <c r="D14" s="28"/>
@@ -1604,7 +1600,7 @@
       <c r="G14" s="28"/>
       <c r="H14" s="26"/>
       <c r="I14" s="26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J14" s="26"/>
       <c r="K14" s="26"/>
@@ -1612,15 +1608,15 @@
       <c r="M14" s="26"/>
       <c r="N14" s="26"/>
     </row>
-    <row r="15" spans="1:26" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="B15" s="27" t="s">
         <v>93</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D15" s="28"/>
       <c r="E15" s="26"/>
@@ -1636,20 +1632,24 @@
       <c r="M15" s="26"/>
       <c r="N15" s="26"/>
     </row>
-    <row r="16" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
         <v>20</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D16" s="28"/>
       <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="28"/>
+      <c r="F16" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>136</v>
+      </c>
       <c r="H16" s="26"/>
       <c r="I16" s="26"/>
       <c r="J16" s="26" t="s">
@@ -1662,20 +1662,20 @@
     </row>
     <row r="17" spans="1:14" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D17" s="28"/>
       <c r="E17" s="26"/>
       <c r="F17" s="26"/>
       <c r="G17" s="28"/>
       <c r="H17" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I17" s="26"/>
       <c r="J17" s="26" t="s">
@@ -1688,13 +1688,13 @@
     </row>
     <row r="18" spans="1:14" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D18" s="28"/>
       <c r="E18" s="26"/>
@@ -1712,20 +1712,20 @@
     </row>
     <row r="19" spans="1:14" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D19" s="28"/>
       <c r="E19" s="26"/>
       <c r="F19" s="26"/>
       <c r="G19" s="28"/>
       <c r="H19" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I19" s="26"/>
       <c r="J19" s="26"/>
@@ -1742,7 +1742,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D20" s="28"/>
       <c r="E20" s="26"/>
@@ -1751,7 +1751,7 @@
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
       <c r="J20" s="26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K20" s="26"/>
       <c r="L20" s="26"/>
@@ -1989,10 +1989,10 @@
         <v>76</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
         <v>61</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="D24" s="13"/>
       <c r="F24" s="21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2366,7 +2366,7 @@
         <v>33</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>94</v>
@@ -2393,19 +2393,19 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="B46" s="20" t="s">
-        <v>99</v>
-      </c>
       <c r="C46" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D46" s="13"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>27</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>28</v>
@@ -2429,7 +2429,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>26</v>

--- a/ONCHO/Entomological survey Survey/Nigeria/2026/ng_oncho_2601_4_b_lab_tar.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2026/ng_oncho_2601_4_b_lab_tar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55E796E-F70C-4EBC-946C-97115F6608EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62954B3-7D49-4E5F-BDBD-38D146B106F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="151">
   <si>
     <t>type</t>
   </si>
@@ -199,9 +199,6 @@
     <t>1. Enter Recorder ID</t>
   </si>
   <si>
-    <t>ng_oncho_2601_4_b_lab_tar</t>
-  </si>
-  <si>
     <t>(Demo) 4. Blackfly Lab App</t>
   </si>
   <si>
@@ -400,9 +397,6 @@
     <t xml:space="preserve">9. Site ID: </t>
   </si>
   <si>
-    <t>10. Please select the months in which the flies included in this pool were collected</t>
-  </si>
-  <si>
     <t>11. How many pools were run from this site for the months indicated?</t>
   </si>
   <si>
@@ -446,6 +440,54 @@
   </si>
   <si>
     <t>The number of pools must between 1 and 200 inclusive</t>
+  </si>
+  <si>
+    <t>ng_oncho_2601_4_b_lab_tar_2</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>10.a. Please select the months in which the flies included in this pool were collected</t>
+  </si>
+  <si>
+    <t>Year must be within a reasonable range</t>
+  </si>
+  <si>
+    <t>yes_no</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>confirm_pools</t>
+  </si>
+  <si>
+    <t>11. You entered ${nb_results} pools. Is this correct?</t>
+  </si>
+  <si>
+    <t>${nb_results} &gt; 0</t>
+  </si>
+  <si>
+    <t>10.b. Please enter the year in which the flies included in this pool were collected</t>
+  </si>
+  <si>
+    <t>. = 'Yes'</t>
+  </si>
+  <si>
+    <t>Please go back and correct the number</t>
+  </si>
+  <si>
+    <t>select_one yes_no</t>
+  </si>
+  <si>
+    <t>. &gt;= 2021 and . &lt;= 2027</t>
+  </si>
+  <si>
+    <t>${confirm_pools} = 'Yes'</t>
   </si>
 </sst>
 </file>
@@ -724,7 +766,117 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="22">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1174,7 +1326,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.625" style="3" customWidth="1"/>
@@ -1283,10 +1435,10 @@
         <v>20</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
@@ -1316,13 +1468,13 @@
     </row>
     <row r="4" spans="1:26" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
@@ -1352,13 +1504,13 @@
     </row>
     <row r="5" spans="1:26" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -1394,7 +1546,7 @@
         <v>34</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D6" s="28"/>
       <c r="E6" s="26"/>
@@ -1412,13 +1564,13 @@
     </row>
     <row r="7" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D7" s="28"/>
       <c r="E7" s="26"/>
@@ -1431,20 +1583,20 @@
       </c>
       <c r="K7" s="26"/>
       <c r="L7" s="26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M7" s="26"/>
       <c r="N7" s="26"/>
     </row>
     <row r="8" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D8" s="28"/>
       <c r="E8" s="26"/>
@@ -1457,20 +1609,20 @@
       </c>
       <c r="K8" s="26"/>
       <c r="L8" s="26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M8" s="26"/>
       <c r="N8" s="26"/>
     </row>
     <row r="9" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D9" s="28"/>
       <c r="E9" s="26"/>
@@ -1494,7 +1646,7 @@
         <v>36</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D10" s="28"/>
       <c r="E10" s="26"/>
@@ -1507,23 +1659,23 @@
       </c>
       <c r="K10" s="26"/>
       <c r="L10" s="26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M10" s="26"/>
       <c r="N10" s="26"/>
     </row>
     <row r="11" spans="1:26" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B11" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="D11" s="28" t="s">
         <v>58</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>59</v>
       </c>
       <c r="E11" s="26"/>
       <c r="F11" s="26"/>
@@ -1543,15 +1695,19 @@
         <v>20</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="D12" s="28"/>
       <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="28"/>
+      <c r="F12" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>138</v>
+      </c>
       <c r="H12" s="26"/>
       <c r="I12" s="26"/>
       <c r="J12" s="26" t="s">
@@ -1563,120 +1719,122 @@
       <c r="N12" s="26"/>
     </row>
     <row r="13" spans="1:26" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29" t="s">
+      <c r="A13" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="27" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>130</v>
+      <c r="C13" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="28"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+    </row>
+    <row r="14" spans="1:26" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
+        <v>148</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="C14" s="28"/>
+        <v>142</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>143</v>
+      </c>
       <c r="D14" s="28"/>
       <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="J14" s="26"/>
+      <c r="F14" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="G14" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26" t="s">
+        <v>9</v>
+      </c>
       <c r="K14" s="26"/>
       <c r="L14" s="26"/>
       <c r="M14" s="26"/>
       <c r="N14" s="26"/>
     </row>
-    <row r="15" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="D15" s="28"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="26"/>
-    </row>
-    <row r="16" spans="1:26" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="26" t="s">
-        <v>20</v>
+    <row r="15" spans="1:26" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="31"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>128</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="28" t="s">
-        <v>133</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C16" s="28"/>
       <c r="D16" s="28"/>
       <c r="E16" s="26"/>
-      <c r="F16" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="G16" s="28" t="s">
-        <v>136</v>
-      </c>
+      <c r="F16" s="26"/>
+      <c r="G16" s="28"/>
       <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26" t="s">
-        <v>9</v>
-      </c>
+      <c r="I16" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="J16" s="26"/>
       <c r="K16" s="26"/>
       <c r="L16" s="26"/>
       <c r="M16" s="26"/>
       <c r="N16" s="26"/>
     </row>
-    <row r="17" spans="1:14" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D17" s="28"/>
       <c r="E17" s="26"/>
       <c r="F17" s="26"/>
       <c r="G17" s="28"/>
-      <c r="H17" s="26" t="s">
-        <v>128</v>
-      </c>
+      <c r="H17" s="26"/>
       <c r="I17" s="26"/>
       <c r="J17" s="26" t="s">
         <v>9</v>
@@ -1688,18 +1846,22 @@
     </row>
     <row r="18" spans="1:14" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="27" t="s">
-        <v>101</v>
-      </c>
       <c r="C18" s="28" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D18" s="28"/>
       <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="28"/>
+      <c r="F18" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>134</v>
+      </c>
       <c r="H18" s="26"/>
       <c r="I18" s="26"/>
       <c r="J18" s="26" t="s">
@@ -1712,37 +1874,39 @@
     </row>
     <row r="19" spans="1:14" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D19" s="28"/>
       <c r="E19" s="26"/>
       <c r="F19" s="26"/>
       <c r="G19" s="28"/>
       <c r="H19" s="26" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
+      <c r="J19" s="26" t="s">
+        <v>9</v>
+      </c>
       <c r="K19" s="26"/>
       <c r="L19" s="26"/>
       <c r="M19" s="26"/>
       <c r="N19" s="26"/>
     </row>
-    <row r="20" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D20" s="28"/>
       <c r="E20" s="26"/>
@@ -1751,70 +1915,118 @@
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
       <c r="J20" s="26" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="K20" s="26"/>
       <c r="L20" s="26"/>
       <c r="M20" s="26"/>
       <c r="N20" s="26"/>
     </row>
-    <row r="21" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="29" t="s">
+    <row r="21" spans="1:14" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="28"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="26"/>
+    </row>
+    <row r="22" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" s="28"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+    </row>
+    <row r="23" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="30"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="29"/>
-    </row>
-    <row r="22" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="26" t="s">
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+    </row>
+    <row r="24" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B24" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-    </row>
-    <row r="23" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+    </row>
+    <row r="25" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B25" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="33"/>
-      <c r="N23" s="33"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1847,10 +2059,10 @@
         <v>34</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1870,13 +2082,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
         <v>42</v>
@@ -1884,13 +2096,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
         <v>42</v>
@@ -1898,13 +2110,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
         <v>42</v>
@@ -1916,142 +2128,142 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2070,7 +2282,7 @@
       </c>
       <c r="D19" s="13"/>
       <c r="F19" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2085,7 +2297,7 @@
       </c>
       <c r="D20" s="13"/>
       <c r="F20" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2100,7 +2312,7 @@
       </c>
       <c r="D21" s="13"/>
       <c r="F21" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2115,7 +2327,7 @@
       </c>
       <c r="D22" s="13"/>
       <c r="F22" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2130,7 +2342,7 @@
       </c>
       <c r="D23" s="13"/>
       <c r="F23" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2145,7 +2357,7 @@
       </c>
       <c r="D24" s="13"/>
       <c r="F24" s="21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2160,7 +2372,7 @@
       </c>
       <c r="D25" s="13"/>
       <c r="F25" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2175,7 +2387,7 @@
       </c>
       <c r="D26" s="13"/>
       <c r="F26" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2190,7 +2402,7 @@
       </c>
       <c r="D27" s="13"/>
       <c r="F27" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2205,7 +2417,7 @@
       </c>
       <c r="D28" s="13"/>
       <c r="F28" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2216,145 +2428,145 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D30" s="13"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D31" s="13"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D32" s="13"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D33" s="13"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D34" s="13"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D35" s="13"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D36" s="13"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D37" s="13"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D38" s="13"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D39" s="13"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D40" s="13"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D41" s="13"/>
     </row>
@@ -2366,10 +2578,10 @@
         <v>33</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D43" s="13"/>
     </row>
@@ -2393,19 +2605,19 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="B46" s="20" t="s">
-        <v>98</v>
-      </c>
       <c r="C46" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D46" s="13"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>27</v>
@@ -2417,7 +2629,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>28</v>
@@ -2429,7 +2641,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>26</v>
@@ -2443,12 +2655,27 @@
       <c r="D50" s="13"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B51" t="s">
+        <v>140</v>
+      </c>
+      <c r="C51" t="s">
+        <v>140</v>
+      </c>
       <c r="D51" s="13"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="11"/>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
+      <c r="A52" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B52" t="s">
+        <v>141</v>
+      </c>
+      <c r="C52" t="s">
+        <v>141</v>
+      </c>
       <c r="D52" s="19"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -3946,32 +4173,32 @@
       <c r="D328" s="13"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+  <conditionalFormatting sqref="B1:B50 B53:B1048576">
+    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53:B147">
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148:B160">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B161:B167">
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19:C28">
-    <cfRule type="duplicateValues" dxfId="2" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218:C263">
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4002,10 +4229,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>19</v>
